--- a/oversikt.xlsx
+++ b/oversikt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatiasGreaker\privat\in3190\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6ADACAA-F407-4CBD-B882-80F0973FA9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026FF44A-9693-4B7B-8313-6982C1B8C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11205" yWindow="690" windowWidth="27300" windowHeight="20295" xr2:uid="{F6556193-E85C-4B33-8988-2896CCC38852}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{F6556193-E85C-4B33-8988-2896CCC38852}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -674,7 +674,8 @@
   <dimension ref="A1:Z14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>

--- a/oversikt.xlsx
+++ b/oversikt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t xml:space="preserve">Uke</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">Project</t>
   </si>
   <si>
+    <t xml:space="preserve">Kommentar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Links:</t>
   </si>
   <si>
@@ -85,6 +88,12 @@
     <t xml:space="preserve">x (20%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Skipper denne nå for å henge
+Med I forelesning.
+Dette kan jeg tross alt ganske bra.
+Kan komme tilbake til dette.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Introduction to project</t>
   </si>
   <si>
@@ -94,10 +103,24 @@
     <t xml:space="preserve">Transform analysis of LTI systems</t>
   </si>
   <si>
+    <t xml:space="preserve">Stopped at “Distortion”</t>
+  </si>
+  <si>
     <t xml:space="preserve"> (0%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Virker som dette handler om å analysere
+LTI systemer. Typisk med en impuls, 
+Step input</t>
+  </si>
+  <si>
     <t xml:space="preserve">Task points (need 48)*:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sampling of continuous signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mangler siste oppgave</t>
   </si>
   <si>
     <t xml:space="preserve">*There will be 12 tasks each with 10 points</t>
@@ -107,8 +130,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -369,28 +393,32 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -398,83 +426,91 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -731,304 +767,325 @@
   <dimension ref="A1:Z14"/>
   <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="33.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="4"/>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="52.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="B8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="20"/>
+      <c r="K8" s="21" t="n">
+        <f aca="false">SUM(E2:E14)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="I10" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="0" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="E3" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" s="9" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="J3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="12"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20" t="n">
-        <f aca="false">SUM(E2:E14)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>13</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B9:C9"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" display="https://tp.educloud.no/uio/app/schedule?semester=25h&amp;scheduleType=course&amp;filterOpen=false&amp;summary=true&amp;pastWeeks=true&amp;tab=teaching&amp;course=IN3190%C2%A41"/>
   </hyperlinks>

--- a/oversikt.xlsx
+++ b/oversikt.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t xml:space="preserve">Uke</t>
   </si>
@@ -73,25 +73,16 @@
     <t xml:space="preserve">Discrete-time signals and systems</t>
   </si>
   <si>
-    <t xml:space="preserve">x (70%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Z-transform</t>
   </si>
   <si>
-    <t xml:space="preserve">x (30%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fourier representation of signal</t>
   </si>
   <si>
-    <t xml:space="preserve">x (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skipper denne nå for å henge
-Med I forelesning.
-Dette kan jeg tross alt ganske bra.
-Kan komme tilbake til dette.</t>
+    <t xml:space="preserve">X (80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Du kan evt. gjøre oppgave 3 for å se på DTFT egenskaper.</t>
   </si>
   <si>
     <t xml:space="preserve">Introduction to project</t>
@@ -118,6 +109,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sampling of continuous signals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">x (70%)</t>
   </si>
   <si>
     <t xml:space="preserve">Mangler siste oppgave</t>
@@ -134,7 +128,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +188,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -585,6 +584,119 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>535680</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>511560</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>82800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Text Frame 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9006480" y="2884320"/>
+          <a:ext cx="2916720" cy="1797120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="ffbf00"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:r>
+            <a:rPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t>Ting jeg kanskje burde se mer på:</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t>* De ulike DTFT/Z-transform egenskapene</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t>* Folding, time-shift etc</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr b="0" lang="nb-NO" sz="1200" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -904,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>10</v>
@@ -933,13 +1045,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>6</v>
@@ -968,16 +1080,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="16"/>
@@ -1003,10 +1115,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1014,19 +1126,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="G8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="I8" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="J8" s="20"/>
       <c r="K8" s="21" t="n">
@@ -1039,17 +1151,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="23" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="24"/>
       <c r="J9" s="25"/>
@@ -1060,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J10" s="28"/>
       <c r="K10" s="29"/>
@@ -1096,5 +1208,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>